--- a/owlcms/src/main/resources/templates/competitionResults/USAW-BARSResults.xlsx
+++ b/owlcms/src/main/resources/templates/competitionResults/USAW-BARSResults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/Misc/usaw-owlcms/local/templates/competitionResults/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D688D01-3CD4-5E4C-A145-AB34EAA840FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9097A74A-2CE8-2941-B9AA-2983E6466D9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="1560" windowWidth="38540" windowHeight="21200" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1460" yWindow="500" windowWidth="39500" windowHeight="24000" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -152,9 +152,6 @@
     <t>Women's 16-17 Age Group</t>
   </si>
   <si>
-    <t>U17 F</t>
-  </si>
-  <si>
     <t>Men's 14-15 Age Group</t>
   </si>
   <si>
@@ -164,9 +161,6 @@
     <t>Women's 14-15 Age Group</t>
   </si>
   <si>
-    <t>U15 F</t>
-  </si>
-  <si>
     <t>Men's 13 Under Age Group</t>
   </si>
   <si>
@@ -176,9 +170,6 @@
     <t>Women's 13 Under Age Group</t>
   </si>
   <si>
-    <t>U13 F</t>
-  </si>
-  <si>
     <t>Junior Men's</t>
   </si>
   <si>
@@ -188,9 +179,6 @@
     <t>Junior Women's</t>
   </si>
   <si>
-    <t>JR F</t>
-  </si>
-  <si>
     <t>Open Men's</t>
   </si>
   <si>
@@ -200,15 +188,9 @@
     <t>Open Women's</t>
   </si>
   <si>
-    <t>Open F</t>
-  </si>
-  <si>
     <t>SR M</t>
   </si>
   <si>
-    <t>SR F</t>
-  </si>
-  <si>
     <t>Men's Masters (35-39)</t>
   </si>
   <si>
@@ -353,27 +335,15 @@
     <t>U25 M</t>
   </si>
   <si>
-    <t>U25 F</t>
-  </si>
-  <si>
     <t>U23 M</t>
   </si>
   <si>
-    <t>U23 F</t>
-  </si>
-  <si>
     <t>U11 M</t>
   </si>
   <si>
-    <t>U11 F</t>
-  </si>
-  <si>
     <t>ADP M</t>
   </si>
   <si>
-    <t>ADP F</t>
-  </si>
-  <si>
     <t>$[VLOOKUP(L2, Validation!$A$1:$B$48,2,FALSE)]</t>
   </si>
   <si>
@@ -402,6 +372,36 @@
   </si>
   <si>
     <t>${athlete.ageGroup}</t>
+  </si>
+  <si>
+    <t>U25 W</t>
+  </si>
+  <si>
+    <t>U23 W</t>
+  </si>
+  <si>
+    <t>U17 W</t>
+  </si>
+  <si>
+    <t>U15 W</t>
+  </si>
+  <si>
+    <t>U13 W</t>
+  </si>
+  <si>
+    <t>U11 W</t>
+  </si>
+  <si>
+    <t>JR W</t>
+  </si>
+  <si>
+    <t>Open W</t>
+  </si>
+  <si>
+    <t>SR W</t>
+  </si>
+  <si>
+    <t>ADP W</t>
   </si>
 </sst>
 </file>
@@ -1151,37 +1151,37 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L2" s="10" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1223,34 +1223,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1263,7 +1263,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1271,340 +1271,340 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B40" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B46" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" s="11" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C47" s="11"/>
       <c r="E47" s="11"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" s="11" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C48" s="11"/>
       <c r="E48" s="11"/>
